--- a/WebDataBase/LabDatabase/static/LabDatabase/DownloadFile/AssemblyPlan.xlsx
+++ b/WebDataBase/LabDatabase/static/LabDatabase/DownloadFile/AssemblyPlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\WebDatabase\WebDataWorld\LabDatabase\static\LabDatabase\DownloadFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26ED715-BA30-42B1-82B9-87EC471C4A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C3579-4DA9-4B5E-B695-87CD863EDD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="5115" windowWidth="17265" windowHeight="9570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16354" yWindow="-103" windowWidth="18720" windowHeight="32520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Part</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,6 +60,94 @@
   </si>
   <si>
     <t>Part End Scar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组装方案名称，同组装结果质粒名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组装结果治理别称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组装层级，1-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元件名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>载体名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质粒名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选填项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wbypsclv7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wbypsclv308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AATG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pScP02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCCT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pscbb23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wby_test1_note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pScORF02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pScTerm02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上传前请务必确认已删除2-6行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlasmidA,PlasmidB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义元件起始scar,如果为标准scar，此列为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义元件终止scar，如果为标准scar，此列为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -83,12 +171,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -103,8 +209,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -385,17 +499,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="33.75" customWidth="1"/>
+    <col min="2" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
+    <col min="6" max="6" width="17.375" customWidth="1"/>
     <col min="7" max="7" width="13.375" customWidth="1"/>
     <col min="8" max="8" width="17.125" customWidth="1"/>
     <col min="9" max="9" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -424,7 +541,115 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:I5"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
